--- a/data/final_predictions/xlsx/pred_Study_3_reviews.xlsx
+++ b/data/final_predictions/xlsx/pred_Study_3_reviews.xlsx
@@ -649,7 +649,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
         <v>6</v>
@@ -730,10 +730,10 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1605,10 +1605,10 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U17" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="U23" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U24" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>6</v>
       </c>
       <c r="U28" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
         <v>6</v>
@@ -2964,10 +2964,10 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3047,10 +3047,10 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>-0</v>
+        <v>0.5</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U38" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>8</v>
       </c>
       <c r="U39" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3837,10 +3837,10 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U42" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>4.5</v>
@@ -4002,7 +4002,7 @@
         <v>7</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4234,10 +4234,10 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -4637,10 +4637,10 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U55" t="n">
         <v>6.5</v>
@@ -4957,10 +4957,10 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -5038,10 +5038,10 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U57" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -5121,10 +5121,10 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
         <v>3</v>
@@ -5356,10 +5356,10 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U62" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>9</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -5672,10 +5672,10 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -5755,10 +5755,10 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
         <v>3</v>
-      </c>
-      <c r="U66" t="n">
-        <v>3.5</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U67" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -5917,10 +5917,10 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -5998,10 +5998,10 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U72" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -6318,10 +6318,10 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U75" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>2</v>
       </c>
       <c r="U77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6804,10 +6804,10 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -6887,10 +6887,10 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U80" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="U81" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U82" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U84" t="n">
         <v>4.5</v>
@@ -7292,10 +7292,10 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U85" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>9</v>
       </c>
       <c r="U86" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -7454,10 +7454,10 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -7535,10 +7535,10 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U88" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -7699,10 +7699,10 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U90" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -7780,10 +7780,10 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U92" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -7944,10 +7944,10 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U94" t="n">
         <v>3.5</v>
@@ -8102,10 +8102,10 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U95" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -8177,10 +8177,10 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -8258,10 +8258,10 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>2</v>
       </c>
       <c r="U98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -8422,10 +8422,10 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U99" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -8501,10 +8501,10 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U100" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -8582,10 +8582,10 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U101" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -8665,10 +8665,10 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -8748,10 +8748,10 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U103" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -8829,10 +8829,10 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U105" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -8993,10 +8993,10 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U106" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U108" t="n">
         <v>5.5</v>
@@ -9230,10 +9230,10 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -9313,10 +9313,10 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U111" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -9475,10 +9475,10 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U112" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -9556,10 +9556,10 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U113" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U114" t="n">
         <v>6.5</v>
@@ -9718,10 +9718,10 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -9799,10 +9799,10 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>9</v>
       </c>
       <c r="U118" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U119" t="n">
         <v>4</v>
@@ -10121,10 +10121,10 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U120" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -10202,10 +10202,10 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U121" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -10285,10 +10285,10 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U122" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -10366,10 +10366,10 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U124" t="n">
         <v>4.5</v>
@@ -10528,10 +10528,10 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>8</v>
       </c>
       <c r="U126" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -10690,10 +10690,10 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U127" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -10771,10 +10771,10 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U128" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -10854,10 +10854,10 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -10929,10 +10929,10 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U130" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -11008,10 +11008,10 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U131" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -11089,10 +11089,10 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U132" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -11170,10 +11170,10 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U133" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>9</v>
       </c>
       <c r="U134" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -11332,10 +11332,10 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U135" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -11413,10 +11413,10 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U136" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -11494,10 +11494,10 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -11575,10 +11575,10 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U139" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -11731,10 +11731,10 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U140" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -11812,10 +11812,10 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U141" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -11893,10 +11893,10 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U142" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -11974,10 +11974,10 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U143" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>8</v>
       </c>
       <c r="U144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -12132,10 +12132,10 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U145" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -12213,10 +12213,10 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U146" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -12294,10 +12294,10 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U147" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -12375,10 +12375,10 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U148" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -12456,10 +12456,10 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U149" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>9</v>
       </c>
       <c r="U150" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -12616,10 +12616,10 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U151" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -12699,10 +12699,10 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U152" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -12780,10 +12780,10 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U153" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>2</v>
       </c>
       <c r="U154" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
@@ -12942,10 +12942,10 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U155" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>9</v>
       </c>
       <c r="U156" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
@@ -13098,10 +13098,10 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U158" t="n">
         <v>6.5</v>
@@ -13256,10 +13256,10 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U159" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V159" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>8</v>
       </c>
       <c r="U160" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
@@ -13418,10 +13418,10 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U161" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
@@ -13499,10 +13499,10 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U162" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="U163" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="U164" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V164" t="inlineStr">
         <is>
@@ -13742,10 +13742,10 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V165" t="inlineStr">
         <is>
@@ -13823,10 +13823,10 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U166" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V166" t="inlineStr">
         <is>
@@ -13904,10 +13904,10 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U167" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
@@ -13985,10 +13985,10 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U168" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V168" t="inlineStr">
         <is>
@@ -14068,10 +14068,10 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U169" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V169" t="inlineStr">
         <is>
@@ -14149,10 +14149,10 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U170" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="V170" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>8</v>
       </c>
       <c r="U171" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
@@ -14311,10 +14311,10 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U172" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -14392,10 +14392,10 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U173" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -14473,10 +14473,10 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U174" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -14554,10 +14554,10 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U175" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -14629,10 +14629,10 @@
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U176" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -14704,10 +14704,10 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U177" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>8</v>
       </c>
       <c r="U178" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="V178" t="inlineStr">
         <is>
@@ -14866,10 +14866,10 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U179" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V179" t="inlineStr">
         <is>
@@ -14947,10 +14947,10 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="n">
+        <v>8</v>
+      </c>
+      <c r="U180" t="n">
         <v>7</v>
-      </c>
-      <c r="U180" t="n">
-        <v>5.5</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -15028,10 +15028,10 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U181" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -15109,10 +15109,10 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U182" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
@@ -15190,10 +15190,10 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U183" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -15271,10 +15271,10 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U184" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U185" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -15429,10 +15429,10 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U186" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
@@ -15510,10 +15510,10 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U187" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
@@ -15589,10 +15589,10 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U188" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -15672,10 +15672,10 @@
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="n">
+        <v>9</v>
+      </c>
+      <c r="U189" t="n">
         <v>8</v>
-      </c>
-      <c r="U189" t="n">
-        <v>5.5</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -15749,10 +15749,10 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U190" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -15826,10 +15826,10 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U191" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -15905,10 +15905,10 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U192" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -15986,10 +15986,10 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U193" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U194" t="n">
         <v>3.5</v>
@@ -16150,10 +16150,10 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U195" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="V195" t="inlineStr">
         <is>
@@ -16233,10 +16233,10 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U196" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
@@ -16318,10 +16318,10 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U197" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
@@ -16399,10 +16399,10 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U198" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U199" t="n">
         <v>2</v>
@@ -16557,10 +16557,10 @@
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U200" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -16638,10 +16638,10 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U201" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
@@ -16723,10 +16723,10 @@
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U202" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -16806,10 +16806,10 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U203" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
@@ -16887,10 +16887,10 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U204" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V204" t="inlineStr">
         <is>
@@ -16968,10 +16968,10 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U205" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V205" t="inlineStr">
         <is>
@@ -17049,10 +17049,10 @@
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U206" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -17130,10 +17130,10 @@
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U207" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>1</v>
       </c>
       <c r="U208" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -17288,10 +17288,10 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U209" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
@@ -17369,10 +17369,10 @@
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U210" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
@@ -17450,10 +17450,10 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U211" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V211" t="inlineStr">
         <is>
@@ -17533,10 +17533,10 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U212" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V212" t="inlineStr">
         <is>
@@ -17614,10 +17614,10 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U213" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V213" t="inlineStr">
         <is>
@@ -17695,10 +17695,10 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U214" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V214" t="inlineStr">
         <is>
@@ -17776,10 +17776,10 @@
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U215" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -17857,10 +17857,10 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U216" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -17938,10 +17938,10 @@
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U217" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U218" t="n">
         <v>7.5</v>
@@ -18103,7 +18103,7 @@
         <v>2</v>
       </c>
       <c r="U219" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -18183,10 +18183,10 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U220" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -18264,10 +18264,10 @@
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U221" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U222" t="n">
         <v>3.5</v>
@@ -18426,10 +18426,10 @@
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U223" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -18511,10 +18511,10 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="n">
+        <v>2</v>
+      </c>
+      <c r="U224" t="n">
         <v>3</v>
-      </c>
-      <c r="U224" t="n">
-        <v>3.5</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -18592,10 +18592,10 @@
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U225" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -18673,10 +18673,10 @@
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="n">
+        <v>9</v>
+      </c>
+      <c r="U226" t="n">
         <v>6</v>
-      </c>
-      <c r="U226" t="n">
-        <v>5.5</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>7</v>
       </c>
       <c r="U227" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -18829,10 +18829,10 @@
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U228" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -18910,10 +18910,10 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U229" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -18993,10 +18993,10 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -19074,10 +19074,10 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U231" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U232" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -19236,10 +19236,10 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U233" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -19311,10 +19311,10 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U234" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U235" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -19467,10 +19467,10 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="n">
+        <v>4</v>
+      </c>
+      <c r="U236" t="n">
         <v>3</v>
-      </c>
-      <c r="U236" t="n">
-        <v>5.5</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U237" t="n">
         <v>4.5</v>
@@ -19631,10 +19631,10 @@
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U238" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -19712,10 +19712,10 @@
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U239" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -19795,10 +19795,10 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V240" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U241" t="n">
         <v>8</v>
@@ -19957,10 +19957,10 @@
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U242" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V242" t="inlineStr">
         <is>
@@ -20038,10 +20038,10 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U243" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="V243" t="inlineStr">
         <is>
@@ -20194,10 +20194,10 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U245" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V245" t="inlineStr">
         <is>
@@ -20275,10 +20275,10 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U246" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V246" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="U247" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V247" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>2</v>
       </c>
       <c r="U248" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -20518,10 +20518,10 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U249" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="V249" t="inlineStr">
         <is>
@@ -20595,10 +20595,10 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V250" t="inlineStr">
         <is>
@@ -20676,10 +20676,10 @@
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
@@ -20757,10 +20757,10 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U252" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
@@ -20838,10 +20838,10 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U253" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
@@ -20919,10 +20919,10 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U254" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V254" t="inlineStr">
         <is>
@@ -21000,10 +21000,10 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U255" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V255" t="inlineStr">
         <is>
@@ -21077,10 +21077,10 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U256" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V256" t="inlineStr">
         <is>
@@ -21162,10 +21162,10 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U257" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V257" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U258" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V258" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U259" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V259" t="inlineStr">
         <is>
@@ -21399,10 +21399,10 @@
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U260" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="V260" t="inlineStr">
         <is>
@@ -21480,10 +21480,10 @@
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V261" t="inlineStr">
         <is>
@@ -21561,10 +21561,10 @@
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U262" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="V262" t="inlineStr">
         <is>
@@ -21636,10 +21636,10 @@
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U263" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V263" t="inlineStr">
         <is>
@@ -21717,10 +21717,10 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U264" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V264" t="inlineStr">
         <is>
@@ -21798,10 +21798,10 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U265" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V265" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>3</v>
       </c>
       <c r="U266" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V266" t="inlineStr">
         <is>
@@ -21960,10 +21960,10 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U267" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V267" t="inlineStr">
         <is>
@@ -22043,10 +22043,10 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U268" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="V268" t="inlineStr">
         <is>
@@ -22124,10 +22124,10 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U269" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V269" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>9</v>
       </c>
       <c r="U270" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="V270" t="inlineStr">
         <is>
@@ -22284,10 +22284,10 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V271" t="inlineStr">
         <is>
@@ -22359,10 +22359,10 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U272" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V272" t="inlineStr">
         <is>
@@ -22440,10 +22440,10 @@
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U273" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V273" t="inlineStr">
         <is>
@@ -22521,10 +22521,10 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U274" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V274" t="inlineStr">
         <is>
@@ -22602,10 +22602,10 @@
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U275" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V275" t="inlineStr">
         <is>
@@ -22681,10 +22681,10 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U276" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V276" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>9</v>
       </c>
       <c r="U277" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V277" t="inlineStr">
         <is>
@@ -22843,10 +22843,10 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr"/>
       <c r="T278" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U278" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V278" t="inlineStr">
         <is>
@@ -22924,10 +22924,10 @@
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U279" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V279" t="inlineStr">
         <is>
@@ -23001,10 +23001,10 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U280" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V280" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U281" t="n">
         <v>4</v>
@@ -23157,7 +23157,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U282" t="n">
         <v>4</v>
@@ -23238,10 +23238,10 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U283" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="V283" t="inlineStr">
         <is>
@@ -23313,10 +23313,10 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U284" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="V284" t="inlineStr">
         <is>
@@ -23394,10 +23394,10 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U285" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="V285" t="inlineStr">
         <is>
@@ -23469,10 +23469,10 @@
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U286" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="V286" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U287" t="n">
         <v>2</v>
@@ -23631,10 +23631,10 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U288" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V288" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U289" t="n">
         <v>3.5</v>
@@ -23793,10 +23793,10 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U290" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V290" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U291" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="V291" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U292" t="n">
         <v>5</v>
@@ -24039,7 +24039,7 @@
         <v>1</v>
       </c>
       <c r="U293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V293" t="inlineStr">
         <is>
@@ -24117,10 +24117,10 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U294" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V294" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
       <c r="R295" t="inlineStr"/>
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U295" t="n">
         <v>2.5</v>
@@ -24273,10 +24273,10 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U296" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V296" t="inlineStr">
         <is>
@@ -24350,10 +24350,10 @@
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U297" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V297" t="inlineStr">
         <is>
@@ -24431,10 +24431,10 @@
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U298" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V298" t="inlineStr">
         <is>
@@ -24512,10 +24512,10 @@
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U299" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="V299" t="inlineStr">
         <is>
@@ -24587,10 +24587,10 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U300" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V300" t="inlineStr">
         <is>
@@ -24668,10 +24668,10 @@
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U301" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V301" t="inlineStr">
         <is>
@@ -24747,10 +24747,10 @@
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr"/>
       <c r="T302" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U302" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="V302" t="inlineStr">
         <is>
@@ -24822,10 +24822,10 @@
       <c r="R303" t="inlineStr"/>
       <c r="S303" t="inlineStr"/>
       <c r="T303" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U303" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="V303" t="inlineStr">
         <is>
@@ -24907,10 +24907,10 @@
       <c r="R304" t="inlineStr"/>
       <c r="S304" t="inlineStr"/>
       <c r="T304" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U304" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V304" t="inlineStr">
         <is>
@@ -24988,10 +24988,10 @@
       <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr"/>
       <c r="T305" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U305" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="V305" t="inlineStr">
         <is>
@@ -25069,10 +25069,10 @@
       <c r="R306" t="inlineStr"/>
       <c r="S306" t="inlineStr"/>
       <c r="T306" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U306" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V306" t="inlineStr">
         <is>
@@ -25150,10 +25150,10 @@
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr"/>
       <c r="T307" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U307" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="V307" t="inlineStr">
         <is>
@@ -25227,10 +25227,10 @@
       <c r="R308" t="inlineStr"/>
       <c r="S308" t="inlineStr"/>
       <c r="T308" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U308" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V308" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
       <c r="R309" t="inlineStr"/>
       <c r="S309" t="inlineStr"/>
       <c r="T309" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U309" t="n">
         <v>6</v>
@@ -25389,10 +25389,10 @@
       <c r="R310" t="inlineStr"/>
       <c r="S310" t="inlineStr"/>
       <c r="T310" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U310" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V310" t="inlineStr">
         <is>
@@ -25470,10 +25470,10 @@
       <c r="R311" t="inlineStr"/>
       <c r="S311" t="inlineStr"/>
       <c r="T311" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U311" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V311" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>9</v>
       </c>
       <c r="U312" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V312" t="inlineStr">
         <is>
@@ -25624,10 +25624,10 @@
       <c r="R313" t="inlineStr"/>
       <c r="S313" t="inlineStr"/>
       <c r="T313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U313" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="V313" t="inlineStr">
         <is>
@@ -25705,10 +25705,10 @@
       <c r="R314" t="inlineStr"/>
       <c r="S314" t="inlineStr"/>
       <c r="T314" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U314" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V314" t="inlineStr">
         <is>
@@ -25786,10 +25786,10 @@
       <c r="R315" t="inlineStr"/>
       <c r="S315" t="inlineStr"/>
       <c r="T315" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V315" t="inlineStr">
         <is>
@@ -25865,10 +25865,10 @@
       <c r="R316" t="inlineStr"/>
       <c r="S316" t="inlineStr"/>
       <c r="T316" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U316" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V316" t="inlineStr">
         <is>
@@ -25946,10 +25946,10 @@
       <c r="R317" t="inlineStr"/>
       <c r="S317" t="inlineStr"/>
       <c r="T317" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U317" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="V317" t="inlineStr">
         <is>
@@ -26023,10 +26023,10 @@
       <c r="R318" t="inlineStr"/>
       <c r="S318" t="inlineStr"/>
       <c r="T318" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U318" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V318" t="inlineStr">
         <is>
@@ -26102,10 +26102,10 @@
       <c r="R319" t="inlineStr"/>
       <c r="S319" t="inlineStr"/>
       <c r="T319" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V319" t="inlineStr">
         <is>
@@ -26183,10 +26183,10 @@
       <c r="R320" t="inlineStr"/>
       <c r="S320" t="inlineStr"/>
       <c r="T320" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U320" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V320" t="inlineStr">
         <is>
@@ -26258,10 +26258,10 @@
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr"/>
       <c r="T321" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U321" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V321" t="inlineStr">
         <is>
@@ -26339,10 +26339,10 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr"/>
       <c r="T322" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U322" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V322" t="inlineStr">
         <is>
@@ -26422,10 +26422,10 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr"/>
       <c r="T323" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U323" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V323" t="inlineStr">
         <is>
@@ -26503,10 +26503,10 @@
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr"/>
       <c r="T324" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U324" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="V324" t="inlineStr">
         <is>
@@ -26578,10 +26578,10 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr"/>
       <c r="T325" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U325" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V325" t="inlineStr">
         <is>
@@ -26659,10 +26659,10 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr"/>
       <c r="T326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U326" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V326" t="inlineStr">
         <is>
@@ -26742,10 +26742,10 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U327" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V327" t="inlineStr">
         <is>
@@ -26823,10 +26823,10 @@
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr"/>
       <c r="T328" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U328" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V328" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
       <c r="R329" t="inlineStr"/>
       <c r="S329" t="inlineStr"/>
       <c r="T329" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U329" t="n">
         <v>6</v>
@@ -26985,10 +26985,10 @@
       <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr"/>
       <c r="T330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U330" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V330" t="inlineStr">
         <is>
@@ -27066,10 +27066,10 @@
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr"/>
       <c r="T331" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U331" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="V331" t="inlineStr">
         <is>
@@ -27147,10 +27147,10 @@
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr"/>
       <c r="T332" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U332" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V332" t="inlineStr">
         <is>
@@ -27230,10 +27230,10 @@
       <c r="R333" t="inlineStr"/>
       <c r="S333" t="inlineStr"/>
       <c r="T333" t="n">
+        <v>2</v>
+      </c>
+      <c r="U333" t="n">
         <v>3</v>
-      </c>
-      <c r="U333" t="n">
-        <v>4</v>
       </c>
       <c r="V333" t="inlineStr">
         <is>
@@ -27307,10 +27307,10 @@
       <c r="R334" t="inlineStr"/>
       <c r="S334" t="inlineStr"/>
       <c r="T334" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U334" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V334" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
       <c r="R335" t="inlineStr"/>
       <c r="S335" t="inlineStr"/>
       <c r="T335" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U335" t="n">
         <v>6</v>
@@ -27469,10 +27469,10 @@
       <c r="R336" t="inlineStr"/>
       <c r="S336" t="inlineStr"/>
       <c r="T336" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U336" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="V336" t="inlineStr">
         <is>
@@ -27544,10 +27544,10 @@
       <c r="R337" t="inlineStr"/>
       <c r="S337" t="inlineStr"/>
       <c r="T337" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U337" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="V337" t="inlineStr">
         <is>
@@ -27625,10 +27625,10 @@
       <c r="R338" t="inlineStr"/>
       <c r="S338" t="inlineStr"/>
       <c r="T338" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U338" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="V338" t="inlineStr">
         <is>
@@ -27704,10 +27704,10 @@
       <c r="R339" t="inlineStr"/>
       <c r="S339" t="inlineStr"/>
       <c r="T339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U339" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V339" t="inlineStr">
         <is>
@@ -27785,10 +27785,10 @@
       <c r="R340" t="inlineStr"/>
       <c r="S340" t="inlineStr"/>
       <c r="T340" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U340" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V340" t="inlineStr">
         <is>
@@ -27866,10 +27866,10 @@
       <c r="R341" t="inlineStr"/>
       <c r="S341" t="inlineStr"/>
       <c r="T341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U341" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V341" t="inlineStr">
         <is>
@@ -27947,10 +27947,10 @@
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr"/>
       <c r="T342" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U342" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V342" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>7</v>
       </c>
       <c r="U343" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V343" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
       <c r="R344" t="inlineStr"/>
       <c r="S344" t="inlineStr"/>
       <c r="T344" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U344" t="n">
         <v>7.5</v>
@@ -28186,7 +28186,7 @@
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr"/>
       <c r="T345" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U345" t="n">
         <v>2.5</v>
@@ -28261,10 +28261,10 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr"/>
       <c r="T346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U346" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V346" t="inlineStr">
         <is>
@@ -28342,10 +28342,10 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr"/>
       <c r="T347" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U347" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V347" t="inlineStr">
         <is>
@@ -28423,10 +28423,10 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr"/>
       <c r="T348" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U348" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="V348" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>3</v>
       </c>
       <c r="U349" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V349" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr"/>
       <c r="T350" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U350" t="n">
         <v>7</v>
@@ -28660,10 +28660,10 @@
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr"/>
       <c r="T351" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U351" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="V351" t="inlineStr">
         <is>
@@ -28735,10 +28735,10 @@
       <c r="R352" t="inlineStr"/>
       <c r="S352" t="inlineStr"/>
       <c r="T352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U352" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V352" t="inlineStr">
         <is>
@@ -28816,10 +28816,10 @@
       <c r="R353" t="inlineStr"/>
       <c r="S353" t="inlineStr"/>
       <c r="T353" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U353" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="V353" t="inlineStr">
         <is>
@@ -28897,10 +28897,10 @@
       <c r="R354" t="inlineStr"/>
       <c r="S354" t="inlineStr"/>
       <c r="T354" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V354" t="inlineStr">
         <is>
@@ -28978,10 +28978,10 @@
       <c r="R355" t="inlineStr"/>
       <c r="S355" t="inlineStr"/>
       <c r="T355" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U355" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="V355" t="inlineStr">
         <is>
@@ -29053,10 +29053,10 @@
       <c r="R356" t="inlineStr"/>
       <c r="S356" t="inlineStr"/>
       <c r="T356" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U356" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V356" t="inlineStr">
         <is>
@@ -29134,10 +29134,10 @@
       <c r="R357" t="inlineStr"/>
       <c r="S357" t="inlineStr"/>
       <c r="T357" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U357" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="V357" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>4</v>
       </c>
       <c r="U358" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="V358" t="inlineStr">
         <is>
@@ -29304,10 +29304,10 @@
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr"/>
       <c r="T359" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U359" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="V359" t="inlineStr">
         <is>
@@ -29389,10 +29389,10 @@
       <c r="R360" t="inlineStr"/>
       <c r="S360" t="inlineStr"/>
       <c r="T360" t="n">
+        <v>9</v>
+      </c>
+      <c r="U360" t="n">
         <v>7</v>
-      </c>
-      <c r="U360" t="n">
-        <v>6</v>
       </c>
       <c r="V360" t="inlineStr">
         <is>
@@ -29470,10 +29470,10 @@
       <c r="R361" t="inlineStr"/>
       <c r="S361" t="inlineStr"/>
       <c r="T361" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U361" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V361" t="inlineStr">
         <is>
@@ -29551,10 +29551,10 @@
       <c r="R362" t="inlineStr"/>
       <c r="S362" t="inlineStr"/>
       <c r="T362" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U362" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V362" t="inlineStr">
         <is>
@@ -29632,10 +29632,10 @@
       <c r="R363" t="inlineStr"/>
       <c r="S363" t="inlineStr"/>
       <c r="T363" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U363" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V363" t="inlineStr">
         <is>
@@ -29715,10 +29715,10 @@
       <c r="R364" t="inlineStr"/>
       <c r="S364" t="inlineStr"/>
       <c r="T364" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U364" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="V364" t="inlineStr">
         <is>
@@ -29794,10 +29794,10 @@
       <c r="R365" t="inlineStr"/>
       <c r="S365" t="inlineStr"/>
       <c r="T365" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U365" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="V365" t="inlineStr">
         <is>
@@ -29875,10 +29875,10 @@
       <c r="R366" t="inlineStr"/>
       <c r="S366" t="inlineStr"/>
       <c r="T366" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U366" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V366" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
       <c r="R367" t="inlineStr"/>
       <c r="S367" t="inlineStr"/>
       <c r="T367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U367" t="n">
         <v>5</v>
@@ -30033,10 +30033,10 @@
       <c r="R368" t="inlineStr"/>
       <c r="S368" t="inlineStr"/>
       <c r="T368" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U368" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="V368" t="inlineStr">
         <is>
@@ -30112,10 +30112,10 @@
       <c r="R369" t="inlineStr"/>
       <c r="S369" t="inlineStr"/>
       <c r="T369" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U369" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V369" t="inlineStr">
         <is>
@@ -30193,10 +30193,10 @@
       <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr"/>
       <c r="T370" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U370" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V370" t="inlineStr">
         <is>
@@ -30274,10 +30274,10 @@
       <c r="R371" t="inlineStr"/>
       <c r="S371" t="inlineStr"/>
       <c r="T371" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U371" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V371" t="inlineStr">
         <is>
@@ -30355,10 +30355,10 @@
       <c r="R372" t="inlineStr"/>
       <c r="S372" t="inlineStr"/>
       <c r="T372" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V372" t="inlineStr">
         <is>
@@ -30436,10 +30436,10 @@
       <c r="R373" t="inlineStr"/>
       <c r="S373" t="inlineStr"/>
       <c r="T373" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U373" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V373" t="inlineStr">
         <is>
@@ -30517,10 +30517,10 @@
       <c r="R374" t="inlineStr"/>
       <c r="S374" t="inlineStr"/>
       <c r="T374" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U374" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V374" t="inlineStr">
         <is>
@@ -30598,10 +30598,10 @@
       <c r="R375" t="inlineStr"/>
       <c r="S375" t="inlineStr"/>
       <c r="T375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U375" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V375" t="inlineStr">
         <is>
@@ -30679,10 +30679,10 @@
       <c r="R376" t="inlineStr"/>
       <c r="S376" t="inlineStr"/>
       <c r="T376" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U376" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="V376" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>9</v>
       </c>
       <c r="U377" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="V377" t="inlineStr">
         <is>
@@ -30837,10 +30837,10 @@
       <c r="R378" t="inlineStr"/>
       <c r="S378" t="inlineStr"/>
       <c r="T378" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U378" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="V378" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
       <c r="R379" t="inlineStr"/>
       <c r="S379" t="inlineStr"/>
       <c r="T379" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U379" t="n">
         <v>5.5</v>
@@ -31001,10 +31001,10 @@
       <c r="R380" t="inlineStr"/>
       <c r="S380" t="inlineStr"/>
       <c r="T380" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U380" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V380" t="inlineStr">
         <is>
@@ -31080,10 +31080,10 @@
       <c r="R381" t="inlineStr"/>
       <c r="S381" t="inlineStr"/>
       <c r="T381" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U381" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V381" t="inlineStr">
         <is>
@@ -31161,10 +31161,10 @@
       <c r="R382" t="inlineStr"/>
       <c r="S382" t="inlineStr"/>
       <c r="T382" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U382" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V382" t="inlineStr">
         <is>
@@ -31242,10 +31242,10 @@
       <c r="R383" t="inlineStr"/>
       <c r="S383" t="inlineStr"/>
       <c r="T383" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U383" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V383" t="inlineStr">
         <is>
@@ -31323,10 +31323,10 @@
       <c r="R384" t="inlineStr"/>
       <c r="S384" t="inlineStr"/>
       <c r="T384" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U384" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="V384" t="inlineStr">
         <is>
@@ -31404,10 +31404,10 @@
       <c r="R385" t="inlineStr"/>
       <c r="S385" t="inlineStr"/>
       <c r="T385" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U385" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="V385" t="inlineStr">
         <is>
@@ -31485,10 +31485,10 @@
       <c r="R386" t="inlineStr"/>
       <c r="S386" t="inlineStr"/>
       <c r="T386" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U386" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="V386" t="inlineStr">
         <is>
@@ -31568,10 +31568,10 @@
       <c r="R387" t="inlineStr"/>
       <c r="S387" t="inlineStr"/>
       <c r="T387" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U387" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="V387" t="inlineStr">
         <is>
@@ -31645,10 +31645,10 @@
       <c r="R388" t="inlineStr"/>
       <c r="S388" t="inlineStr"/>
       <c r="T388" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U388" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="V388" t="inlineStr">
         <is>
@@ -31726,10 +31726,10 @@
       <c r="R389" t="inlineStr"/>
       <c r="S389" t="inlineStr"/>
       <c r="T389" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U389" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V389" t="inlineStr">
         <is>
@@ -31807,10 +31807,10 @@
       <c r="R390" t="inlineStr"/>
       <c r="S390" t="inlineStr"/>
       <c r="T390" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U390" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V390" t="inlineStr">
         <is>
@@ -31888,10 +31888,10 @@
       <c r="R391" t="inlineStr"/>
       <c r="S391" t="inlineStr"/>
       <c r="T391" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U391" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V391" t="inlineStr">
         <is>
@@ -31969,10 +31969,10 @@
       <c r="R392" t="inlineStr"/>
       <c r="S392" t="inlineStr"/>
       <c r="T392" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U392" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="V392" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>2</v>
       </c>
       <c r="U393" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V393" t="inlineStr">
         <is>
